--- a/src/data/downloads/2024_elections_to_the_Supreme_Council_of_the_Autonomous_Repu_main_20241026_data_202604222211119.xlsx
+++ b/src/data/downloads/2024_elections_to_the_Supreme_Council_of_the_Autonomous_Repu_main_20241026_data_202604222211119.xlsx
@@ -7,14 +7,14 @@
     <sheet sheetId="1" name="PR - Precincts" state="visible" r:id="rId4"/>
     <sheet sheetId="2" name="PR - Districts" state="visible" r:id="rId5"/>
     <sheet sheetId="3" name="Candidates - კანდიდატები" state="visible" r:id="rId6"/>
-    <sheet sheetId="4" name="About - მეტამონაცემები" state="visible" r:id="rId7"/>
+    <sheet sheetId="4" name="About - Metadata" state="visible" r:id="rId7"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1736" uniqueCount="719">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1726" uniqueCount="715">
   <si>
     <t xml:space="preserve">Precinct ID
 საარჩ. კოდი</t>
@@ -2152,13 +2152,13 @@
     <t>Archive</t>
   </si>
   <si>
-    <t>Comprehensive Election Data Archive of Georgia (CEDAG)</t>
+    <t>Georgia Election Data Archive (GEDA)</t>
   </si>
   <si>
     <t>Website</t>
   </si>
   <si>
-    <t>https://electionsdata.ge</t>
+    <t>https://electionsdata.ge/elections?type=adjara&amp;election=adj_2024</t>
   </si>
   <si>
     <t>Author</t>
@@ -2167,77 +2167,65 @@
     <t>David Sichinava</t>
   </si>
   <si>
+    <t>Election (EN)</t>
+  </si>
+  <si>
+    <t>2024 elections to the Supreme Council of the Autonomous Republic of Adjara</t>
+  </si>
+  <si>
+    <t>Election (KA)</t>
+  </si>
+  <si>
+    <t>აჭარის ავტონომიური რესპუბლიკის უმაღლესი საბჭოს 2024 წლის არჩევნები</t>
+  </si>
+  <si>
+    <t>Election ID</t>
+  </si>
+  <si>
+    <t>adj_2024</t>
+  </si>
+  <si>
+    <t>Election Type</t>
+  </si>
+  <si>
+    <t>adjara</t>
+  </si>
+  <si>
+    <t>Election Date</t>
+  </si>
+  <si>
+    <t>2024-10-26</t>
+  </si>
+  <si>
+    <t>File Generated</t>
+  </si>
+  <si>
+    <t>2026-04-30T18:50:28.616Z</t>
+  </si>
+  <si>
+    <t>Data Source</t>
+  </si>
+  <si>
+    <t>Freedom of Information (FOI) request from the Supreme Electoral Council of Adjara</t>
+  </si>
+  <si>
     <t>Citation (APA)</t>
   </si>
   <si>
-    <t>Sichinava, D. (2026). Results of the 2024 elections to the Supreme Council of the Autonomous Republic of Adjara. Comprehensive Election Data Archive of Georgia (CEDAG). https://electionsdata.ge/adj_2024</t>
-  </si>
-  <si>
-    <t>Citation (Chicago)</t>
-  </si>
-  <si>
-    <t>Sichinava, David. 2026. "Results of the 2024 elections to the Supreme Council of the Autonomous Republic of Adjara." Comprehensive Election Data Archive of Georgia (CEDAG). https://electionsdata.ge/adj_2024.</t>
-  </si>
-  <si>
-    <t>Election (EN)</t>
-  </si>
-  <si>
-    <t>2024 elections to the Supreme Council of the Autonomous Republic of Adjara</t>
-  </si>
-  <si>
-    <t>Election (KA)</t>
-  </si>
-  <si>
-    <t>აჭარის ავტონომიური რესპუბლიკის უმაღლესი საბჭოს 2024 წლის არჩევნები</t>
-  </si>
-  <si>
-    <t>Election ID</t>
-  </si>
-  <si>
-    <t>adj_2024</t>
-  </si>
-  <si>
-    <t>Election Type</t>
-  </si>
-  <si>
-    <t>adjara</t>
-  </si>
-  <si>
-    <t>Election Date</t>
-  </si>
-  <si>
-    <t>2024-10-26</t>
-  </si>
-  <si>
-    <t>Sub-election</t>
-  </si>
-  <si>
-    <t>Main Election</t>
-  </si>
-  <si>
-    <t>File Generated</t>
-  </si>
-  <si>
-    <t>2026-04-22T22:11:11.978Z</t>
-  </si>
-  <si>
-    <t>Data Source</t>
-  </si>
-  <si>
-    <t>Central Election Commission of Georgia (cesko.ge)</t>
+    <t>Sichinava, D. (2026). Results of the 2024 elections to the Supreme Council of the Autonomous Republic of Adjara. Georgia Election Data Archive (GEDA). https://electionsdata.ge/elections?type=adjara&amp;election=adj_2024</t>
   </si>
   <si>
     <t>License</t>
   </si>
   <si>
-    <t>Open data. Please cite CEDAG when using.</t>
+    <t>CC-BY-4.0</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -2260,10 +2248,6 @@
       <sz val="9"/>
     </font>
     <font>
-      <sz val="9"/>
-    </font>
-    <font>
-      <i/>
       <sz val="9"/>
     </font>
   </fonts>
@@ -2301,7 +2285,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2309,9 +2293,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -39675,7 +39656,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -40424,7 +40405,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -40509,17 +40490,17 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="72" customWidth="1"/>
+    <col min="2" max="2" width="88" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -40550,7 +40531,7 @@
       <c r="A4" s="3" t="s">
         <v>697</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="4" t="s">
         <v>698</v>
       </c>
     </row>
@@ -40563,99 +40544,59 @@
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>206</v>
+      <c r="A6" s="3" t="s">
+        <v>701</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>206</v>
+        <v>702</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>712</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>206</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
-        <v>713</v>
-      </c>
-      <c r="B14" s="4" t="s">
         <v>714</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
-        <v>715</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>716</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>206</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
-        <v>717</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>718</v>
       </c>
     </row>
   </sheetData>

--- a/src/data/downloads/2024_elections_to_the_Supreme_Council_of_the_Autonomous_Repu_main_20241026_data_202604222211119.xlsx
+++ b/src/data/downloads/2024_elections_to_the_Supreme_Council_of_the_Autonomous_Repu_main_20241026_data_202604222211119.xlsx
@@ -2200,7 +2200,7 @@
     <t>File Generated</t>
   </si>
   <si>
-    <t>2026-04-30T18:50:28.616Z</t>
+    <t>2026-05-12T18:52:42.649Z</t>
   </si>
   <si>
     <t>Data Source</t>
